--- a/KatalonData/IVT/IVT_SameJSON_UI.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_UI.xlsx
@@ -3,27 +3,26 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE6483E-82B5-47E9-AA0A-2BF390120B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CDCA65-596D-46C6-9993-54A24611B906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson_Ui" sheetId="2" r:id="rId1"/>
     <sheet name="ParcelsLabel_SameJson_Ui" sheetId="6" r:id="rId2"/>
     <sheet name="EMV_SameJson_Ui" sheetId="7" r:id="rId3"/>
     <sheet name="CreditDebitCard_SameJson_Ui" sheetId="8" r:id="rId4"/>
-    <sheet name="PersonalChecking_SameJson_Ui" sheetId="10" r:id="rId5"/>
-    <sheet name="PersonalSavings_SameJson_Ui" sheetId="11" r:id="rId6"/>
-    <sheet name="BusinessChecking_SameJson_Ui" sheetId="12" r:id="rId7"/>
+    <sheet name="PersonalCheckSave_SameJson_Ui" sheetId="10" r:id="rId5"/>
+    <sheet name="BusinessChecking_SameJson_Ui" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="20">
   <si>
     <t>Result</t>
   </si>
@@ -123,17 +122,32 @@
 'Parcels Label' page, 'Amount', Parcel table data</t>
   </si>
   <si>
-    <t>Mon Sep 07 23:30:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Verifying-
-'EMV Cloud Terminal' fields values</t>
+    <t>Tue Sep 08 21:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 20:16:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 20:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 20:59:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 21:01:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 10 21:03:31 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -569,13 +583,13 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.7265625" style="7" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -645,10 +659,10 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="21.08984375" customWidth="1"/>
-    <col min="3" max="3" width="46.7265625" customWidth="1"/>
-    <col min="5" max="5" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="11.0"/>
+    <col min="2" max="2" customWidth="true" width="21.08984375"/>
+    <col min="3" max="3" customWidth="true" width="46.7265625"/>
+    <col min="5" max="5" customWidth="true" width="25.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -692,13 +706,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2E93B6-AED7-4CE5-8867-1E7A9966B5E7}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="32.26953125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,19 +732,52 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="C2" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -733,36 +786,240 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B395BBDF-ACD5-4248-8AE5-014892F4125E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7982227C-0283-439A-A797-C382419F435A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6156-0356-42C9-AC08-28C6664C517D}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04532628-18FA-4C04-BD27-113F298023B2}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04532628-18FA-4C04-BD27-113F298023B2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/IVT/IVT_SameJSON_UI.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_UI.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
   <si>
     <t>Result</t>
   </si>
@@ -147,6 +147,42 @@
   </si>
   <si>
     <t>Fri Sep 18 15:53:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 18 23:28:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:05:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:18:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:20:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:22:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:25:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:34:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 18:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 18:55:20 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -746,10 +782,10 @@
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -829,7 +865,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -909,7 +945,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -989,7 +1025,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>

--- a/KatalonData/IVT/IVT_SameJSON_UI.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_UI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5660C5A7-E46D-4789-B286-02EE9B7944E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF3C153-5A47-4BF5-829A-13C0F702A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="7" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson_Ui" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="CreditDebitCard_SameJson_Ui" sheetId="8" r:id="rId4"/>
     <sheet name="PersonalCheckSave_SameJson_Ui" sheetId="10" r:id="rId5"/>
     <sheet name="BusinessChecking_SameJson_Ui" sheetId="12" r:id="rId6"/>
+    <sheet name="CreditCard_SameJson_Ui" sheetId="13" r:id="rId7"/>
+    <sheet name="DebitCard_SameJson_Ui" sheetId="14" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="63">
   <si>
     <t>Result</t>
   </si>
@@ -122,67 +124,154 @@
 'Parcels Label' page, 'Amount', Parcel table data</t>
   </si>
   <si>
-    <t>Tue Sep 08 21:19:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 20:16:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 20:55:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 21:01:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 10 21:03:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 13:12:16 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Sep 18 13:48:16 IST 2026</t>
   </si>
   <si>
+    <t>Mon Sep 21 20:34:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 21 20:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 18:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 18:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>CardNo</t>
+  </si>
+  <si>
+    <t>ExpMM</t>
+  </si>
+  <si>
+    <t>ExpYYYY</t>
+  </si>
+  <si>
+    <t>SecurityCode</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Zip</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>UDF1</t>
+  </si>
+  <si>
+    <t>UDF2</t>
+  </si>
+  <si>
+    <t>UDF3</t>
+  </si>
+  <si>
+    <t>UDF4</t>
+  </si>
+  <si>
+    <t>UDF5</t>
+  </si>
+  <si>
+    <t>UDF6</t>
+  </si>
+  <si>
+    <t>UDF7</t>
+  </si>
+  <si>
+    <t>UDF8</t>
+  </si>
+  <si>
+    <t>UDF9</t>
+  </si>
+  <si>
+    <t>UDF10</t>
+  </si>
+  <si>
+    <t>4761730000000011</t>
+  </si>
+  <si>
+    <t>6510000000000216</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 18:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>2222400060000007</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>2223520443560010</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:26:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 16:30:40 IST 2026</t>
+  </si>
+  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Fri Sep 18 15:53:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 23:28:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:05:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:16:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:18:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:20:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:22:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:25:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:31:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:34:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Sep 21 20:51:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 18:48:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 18:55:20 IST 2026</t>
+    <t>Mon Oct 05 17:58:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:08:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:11:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:14:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:24:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:31:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:39:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 18:54:17 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -190,7 +279,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -223,13 +312,32 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -256,10 +364,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -288,8 +397,27 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -729,7 +857,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>12</v>
@@ -785,7 +913,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -865,7 +993,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -945,7 +1073,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -1025,7 +1153,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -1060,6 +1188,312 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396BC418-5ECC-4CA1-A625-D713C495CCC5}">
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
+    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" style="4" width="8.7265625"/>
+    <col min="5" max="5" customWidth="true" style="12" width="18.36328125"/>
+    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
+    <col min="7" max="7" style="4" width="8.7265625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
+    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
+    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
+    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
+    <col min="19" max="16384" style="4" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H2" s="4">
+        <v>201</v>
+      </c>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H3" s="4">
+        <v>201</v>
+      </c>
+      <c r="J3" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF146541-D81D-415C-B9DC-463A61EC9F50}">
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
+    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" style="4" width="8.7265625"/>
+    <col min="5" max="5" customWidth="true" style="12" width="18.36328125"/>
+    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
+    <col min="7" max="7" style="4" width="8.7265625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
+    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
+    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
+    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
+    <col min="19" max="16384" style="4" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2030</v>
+      </c>
+      <c r="H2" s="4">
+        <v>737</v>
+      </c>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H3" s="4">
+        <v>345</v>
+      </c>
+      <c r="J3" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/KatalonData/IVT/IVT_SameJSON_UI.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_UI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF3C153-5A47-4BF5-829A-13C0F702A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7CC13D-20E5-48C8-BFCE-4B948A50DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="5" activeTab="7" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="9" activeTab="10" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson_Ui" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="BusinessChecking_SameJson_Ui" sheetId="12" r:id="rId6"/>
     <sheet name="CreditCard_SameJson_Ui" sheetId="13" r:id="rId7"/>
     <sheet name="DebitCard_SameJson_Ui" sheetId="14" r:id="rId8"/>
+    <sheet name="BusinessCheck_SameJson_Ui" sheetId="16" r:id="rId9"/>
+    <sheet name="PersonalCheck_SameJson_Ui" sheetId="17" r:id="rId10"/>
+    <sheet name="PersonalSav_SameJson_Ui" sheetId="18" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="75">
   <si>
     <t>Result</t>
   </si>
@@ -130,15 +133,6 @@
     <t>Mon Sep 21 20:34:35 IST 2026</t>
   </si>
   <si>
-    <t>Mon Sep 21 20:51:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 18:48:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 18:55:20 IST 2026</t>
-  </si>
-  <si>
     <t>CardNo</t>
   </si>
   <si>
@@ -214,9 +208,6 @@
     <t>09</t>
   </si>
   <si>
-    <t>Wed Sep 30 18:59:26 IST 2026</t>
-  </si>
-  <si>
     <t>2222400060000007</t>
   </si>
   <si>
@@ -229,49 +220,97 @@
     <t>11</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed Sep 30 22:26:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 16:30:40 IST 2026</t>
+    <t>Mon Oct 05 18:54:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 19:13:01 IST 2026</t>
+  </si>
+  <si>
+    <t>RoutingNo</t>
+  </si>
+  <si>
+    <t>AccountNo</t>
+  </si>
+  <si>
+    <t>ConfirmAccNo</t>
+  </si>
+  <si>
+    <t>BusinessName</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>256072691</t>
+  </si>
+  <si>
+    <t>95125489</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 13:32:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 18:01:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 18:05:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 18:08:07 IST 2026</t>
+  </si>
+  <si>
+    <t>AccType</t>
+  </si>
+  <si>
+    <t>65987541</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>1234567</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 21:27:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 13:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Savings</t>
+  </si>
+  <si>
+    <t>12345</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Mon Oct 05 17:58:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:04:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:08:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:11:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:14:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:24:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:31:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:36:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:39:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:42:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Oct 05 18:54:17 IST 2026</t>
+    <t>Thu Oct 08 21:52:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 21:53:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 11:42:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 12:01:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 12:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 12:22:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 12:25:50 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -320,7 +359,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +375,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -414,6 +459,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -824,6 +875,338 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8385B2-BD57-4A85-BDDD-DBF8A2A044B4}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="12" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="9.90625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740E0693-B35A-4392-9E39-4990DA74D260}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="12" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="9.90625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01403168-705F-4462-A713-D615A4BFC50C}">
   <dimension ref="A1:E2"/>
@@ -993,7 +1376,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -1073,7 +1456,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -1153,7 +1536,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -1234,73 +1617,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="X1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="Y1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="Z1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -1308,13 +1691,13 @@
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4">
         <v>12</v>
@@ -1329,10 +1712,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -1387,90 +1770,90 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="X1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="Y1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="Z1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="4">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G2" s="4">
         <v>2030</v>
@@ -1482,10 +1865,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -1494,6 +1877,169 @@
         <v>345</v>
       </c>
       <c r="J3" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C190F92-BAC0-4017-8467-B4569825A802}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="12" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="13.7265625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/KatalonData/IVT/IVT_SameJSON_UI.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_UI.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="76">
   <si>
     <t>Result</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Fri Oct 09 12:25:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 12:27:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1694,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
